--- a/public/tridy.xlsx
+++ b/public/tridy.xlsx
@@ -1,49 +1,371 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\instaluju\Documents\Motol\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{343CE413-61E3-4ACA-A3CA-A780039FA0C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="6810" yWindow="1020" windowWidth="12050" windowHeight="10410" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet name="1.A" sheetId="1" r:id="rId1"/>
-    <sheet name="2.B" sheetId="2" r:id="rId2"/>
-    <sheet name="Sekunda" sheetId="3" r:id="rId3"/>
+    <sheet name="3A" sheetId="2" r:id="rId1"/>
+    <sheet name="1E" sheetId="3" r:id="rId2"/>
+    <sheet name="3A_a" sheetId="4" r:id="rId3"/>
+    <sheet name="3A_b" sheetId="5" r:id="rId4"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="108">
+  <si>
+    <t>Jméno a příjmení</t>
+  </si>
+  <si>
+    <t>Adam Brož</t>
+  </si>
+  <si>
+    <t>Anastasiia Balanets</t>
+  </si>
+  <si>
+    <t>Antonín Povolný</t>
+  </si>
+  <si>
+    <t>Daniel Horáček</t>
+  </si>
+  <si>
+    <t>Dominik Pavelka</t>
+  </si>
+  <si>
+    <t>Hynek Mayrhofer</t>
+  </si>
+  <si>
+    <t>Jakub Suchánsky</t>
+  </si>
+  <si>
+    <t>Jáchym Viták</t>
+  </si>
+  <si>
+    <t>Karyna Kryvka</t>
+  </si>
+  <si>
+    <t>Kubát Pavel</t>
+  </si>
+  <si>
+    <t>Lukáš Jiránek</t>
+  </si>
+  <si>
+    <t>Maksym Kravets</t>
+  </si>
+  <si>
+    <t>Marek Miláček</t>
+  </si>
+  <si>
+    <t>Marek Řehák</t>
+  </si>
+  <si>
+    <t>Mark Nahornyi</t>
+  </si>
+  <si>
+    <t>Matyáš Sauer</t>
+  </si>
+  <si>
+    <t>Michael Bartuněk</t>
+  </si>
+  <si>
+    <t>Michal Hron</t>
+  </si>
+  <si>
+    <t>Mykola Mandziuk</t>
+  </si>
+  <si>
+    <t>Ondřej Borovička</t>
+  </si>
+  <si>
+    <t>Petr Škarvan</t>
+  </si>
+  <si>
+    <t>Tomáš Filip</t>
+  </si>
+  <si>
+    <t>Tomáš Jandák</t>
+  </si>
+  <si>
+    <t>Tomáš Sunkovský</t>
+  </si>
+  <si>
+    <t>Tomáš Štěpán</t>
+  </si>
+  <si>
+    <t>Vincent Procházka</t>
+  </si>
+  <si>
+    <t>Vitalii Fenynets</t>
+  </si>
+  <si>
+    <t>Vojtěch Garčic</t>
+  </si>
+  <si>
+    <t>Šimon Kreperát</t>
+  </si>
+  <si>
+    <t>Šimon Kubala</t>
+  </si>
+  <si>
+    <t>David Sládeček</t>
+  </si>
+  <si>
+    <t>Filip Rahbani</t>
+  </si>
+  <si>
+    <t>Hugo Struček</t>
+  </si>
+  <si>
+    <t>Jakub Zvěřina</t>
+  </si>
+  <si>
+    <t>Jan Brandejs</t>
+  </si>
+  <si>
+    <t>Lukáš Vojáček</t>
+  </si>
+  <si>
+    <t>Maksym Pavlyk</t>
+  </si>
+  <si>
+    <t>Martin Krkoška</t>
+  </si>
+  <si>
+    <t>Martin Stržínek</t>
+  </si>
+  <si>
+    <t>Michael Brychta</t>
+  </si>
+  <si>
+    <t>Mikuláš Hejnyš</t>
+  </si>
+  <si>
+    <t>Ondřej Vošahlík</t>
+  </si>
+  <si>
+    <t>Samuel Hrabák</t>
+  </si>
+  <si>
+    <t>Tereza Tichá</t>
+  </si>
+  <si>
+    <t>Timotej Goliáš</t>
+  </si>
+  <si>
+    <t>Tomáš Kučera</t>
+  </si>
+  <si>
+    <t>Tomáš Vorel</t>
+  </si>
+  <si>
+    <t>Viktor Bečka</t>
+  </si>
+  <si>
+    <t>Vojtěch Mládek</t>
+  </si>
+  <si>
+    <t>Vojtěch Valášek</t>
+  </si>
+  <si>
+    <t>Yehor Sablin</t>
+  </si>
+  <si>
+    <t>Zdeněk Dvořák</t>
+  </si>
+  <si>
+    <t>Anastasiia</t>
+  </si>
+  <si>
+    <t>Balanets</t>
+  </si>
+  <si>
+    <t>Michael</t>
+  </si>
+  <si>
+    <t>Bartuněk</t>
+  </si>
+  <si>
+    <t>Ondřej</t>
+  </si>
+  <si>
+    <t>Borovička</t>
+  </si>
+  <si>
+    <t>Adam</t>
+  </si>
+  <si>
+    <t>Brož</t>
+  </si>
+  <si>
+    <t>Vitalii</t>
+  </si>
+  <si>
+    <t>Fenynets</t>
+  </si>
+  <si>
+    <t>Tomáš</t>
+  </si>
+  <si>
+    <t>Filip</t>
+  </si>
+  <si>
+    <t>Vojtěch</t>
+  </si>
+  <si>
+    <t>Garčic</t>
+  </si>
+  <si>
+    <t>Daniel</t>
+  </si>
+  <si>
+    <t>Horáček</t>
+  </si>
+  <si>
+    <t>Michal</t>
+  </si>
+  <si>
+    <t>Hron</t>
+  </si>
+  <si>
+    <t>Jandák</t>
+  </si>
+  <si>
+    <t>Lukáš</t>
+  </si>
+  <si>
+    <t>Jiránek</t>
+  </si>
+  <si>
+    <t>Maksym</t>
+  </si>
+  <si>
+    <t>Kravets</t>
+  </si>
+  <si>
+    <t>Šimon</t>
+  </si>
+  <si>
+    <t>Kreperát</t>
+  </si>
+  <si>
+    <t>Karyna</t>
+  </si>
+  <si>
+    <t>Kryvka</t>
+  </si>
+  <si>
+    <t>Kubala</t>
+  </si>
+  <si>
+    <t>Kubát</t>
+  </si>
+  <si>
+    <t>Pavel</t>
+  </si>
+  <si>
+    <t>Mykola</t>
+  </si>
+  <si>
+    <t>Mandziuk</t>
+  </si>
+  <si>
+    <t>Hynek</t>
+  </si>
+  <si>
+    <t>Mayrhofer</t>
+  </si>
+  <si>
+    <t>Marek</t>
+  </si>
+  <si>
+    <t>Miláček</t>
+  </si>
+  <si>
+    <t>Mark</t>
+  </si>
+  <si>
+    <t>Nahornyi</t>
+  </si>
+  <si>
+    <t>Dominik</t>
+  </si>
+  <si>
+    <t>Pavelka</t>
+  </si>
+  <si>
+    <t>Antonín</t>
+  </si>
+  <si>
+    <t>Povolný</t>
+  </si>
+  <si>
+    <t>Vincent</t>
+  </si>
+  <si>
+    <t>Procházka</t>
+  </si>
+  <si>
+    <t>Řehák</t>
+  </si>
+  <si>
+    <t>Matyáš</t>
+  </si>
+  <si>
+    <t>Sauer</t>
+  </si>
+  <si>
+    <t>Jakub</t>
+  </si>
+  <si>
+    <t>Suchánsky</t>
+  </si>
+  <si>
+    <t>Sunkovský</t>
+  </si>
+  <si>
+    <t>Petr</t>
+  </si>
+  <si>
+    <t>Škarvan</t>
+  </si>
+  <si>
+    <t>Štěpán</t>
+  </si>
+  <si>
+    <t>Jáchym</t>
+  </si>
+  <si>
+    <t>Viták</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="2">
@@ -54,7 +376,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -62,18 +384,42 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normální" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -398,198 +744,580 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:A31"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="25.83203125" customWidth="1"/>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Jméno a příjmení</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Tereza Černá</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Adam Dvořák</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Filip Horák</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Eliška Kučerová</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Matyáš Marek</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Viktorie Nováková</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Jan Pospíšil</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Sofie Procházková</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>David Svoboda</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Adéla Veselá</v>
+    <row r="1" spans="1:1" ht="15.5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="15.5">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="15.5">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="15.5">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="15.5">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="15.5">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="15.5">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="15.5">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="15.5">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="15.5">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="15.5">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="15.5">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="15.5">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="15.5">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="15.5">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="15.5">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="15.5">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="15.5">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="15.5">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="15.5">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="15.5">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="15.5">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="15.5">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="15.5">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="15.5">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="15.5">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="15.5">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="15.5">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" ht="15.5">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" ht="15.5">
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="15.5">
+      <c r="A31" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A11"/>
+    <ignoredError sqref="A1:A31" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:A23"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="25.83203125" customWidth="1"/>
+    <col min="1" max="1" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Jméno a příjmení</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Jakub Bartoš</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Kristýna Blažková</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Daniel Čermák</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Karolína Fialová</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Lukáš Holub</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Natálie Janda</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Tomáš Král</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Aneta Malá</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Ondřej Němec</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Barbora Růžičková</v>
+    <row r="1" spans="1:1" ht="15.5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="15.5">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="15.5">
+      <c r="A3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="15.5">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="15.5">
+      <c r="A5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="15.5">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="15.5">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="15.5">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="15.5">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="15.5">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="15.5">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="15.5">
+      <c r="A12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="15.5">
+      <c r="A13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="15.5">
+      <c r="A14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="15.5">
+      <c r="A15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="15.5">
+      <c r="A16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="15.5">
+      <c r="A17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="15.5">
+      <c r="A18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="15.5">
+      <c r="A19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="15.5">
+      <c r="A20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="15.5">
+      <c r="A21" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="15.5">
+      <c r="A22" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="15.5">
+      <c r="A23" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A11"/>
+    <ignoredError sqref="A1:A23" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE469823-409F-4510-9D6D-062E831698A5}">
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultRowHeight="15.5"/>
   <cols>
-    <col min="1" max="1" width="25.83203125" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Jméno a příjmení</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Vojtěch Beneš</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Klára Doležalová</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Martin Jelínek</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Lucie Křížová</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Matěj Moravec</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Anna Pokorná</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Štěpán Sedláček</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Ema Šimková</v>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="17.5">
+      <c r="A2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="17.5">
+      <c r="A3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="17.5">
+      <c r="A4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="17.5">
+      <c r="A5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="17.5">
+      <c r="A6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="17.5">
+      <c r="A7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="17.5">
+      <c r="A8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="17.5">
+      <c r="A9" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="17.5">
+      <c r="A10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="17.5">
+      <c r="A11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="17.5">
+      <c r="A12" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="17.5">
+      <c r="A13" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="17.5">
+      <c r="A14" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="17.5">
+      <c r="A15" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="17.5">
+      <c r="A16" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="17.5">
+      <c r="A17" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A9"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E4113AD-B323-4242-B71C-08EA5415FB9F}">
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr defaultRowHeight="15.5"/>
+  <cols>
+    <col min="1" max="1" width="9.58203125" customWidth="1"/>
+    <col min="2" max="2" width="11.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="17.5">
+      <c r="A2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="17.5">
+      <c r="A3" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="17.5">
+      <c r="A4" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="17.5">
+      <c r="A5" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="17.5">
+      <c r="A6" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="17.5">
+      <c r="A7" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="17.5">
+      <c r="A8" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="17.5">
+      <c r="A9" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="17.5">
+      <c r="A10" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="17.5">
+      <c r="A11" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="17.5">
+      <c r="A12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="17.5">
+      <c r="A13" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="17.5">
+      <c r="A14" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="17.5">
+      <c r="A15" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>